--- a/output/pdf_financials_xlsx/GDL.xlsx
+++ b/output/pdf_financials_xlsx/GDL.xlsx
@@ -1952,37 +1952,37 @@
         <v>0.86</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.965</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.703</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.622</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.578</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.578</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>4.253</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>4.253</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>28.379</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>5.314</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>3.767</v>
       </c>
     </row>
     <row r="35">
@@ -2044,37 +2044,37 @@
         <v>0.86</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.965</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.703</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.622</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.578</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>2.578</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>4.253</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>4.253</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>28.379</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>5.314</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>3.767</v>
       </c>
     </row>
     <row r="37">
@@ -2596,37 +2596,37 @@
         <v>3.271</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>5.121</v>
+        <v>4.156</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>12.164</v>
+        <v>11.461</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>6.046</v>
+        <v>4.424</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>5.721</v>
+        <v>3.143</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>5.721</v>
+        <v>3.143</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>8.442</v>
+        <v>4.189</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>8.442</v>
+        <v>4.189</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>8.414</v>
+        <v>4.994</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>38.88</v>
+        <v>10.501</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>15.995</v>
+        <v>10.681</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>8.295</v>
+        <v>4.528</v>
       </c>
     </row>
     <row r="49">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">

--- a/output/pdf_financials_xlsx/GDL.xlsx
+++ b/output/pdf_financials_xlsx/GDL.xlsx
@@ -5523,43 +5523,43 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.068</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.096</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>1.585</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.147</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.576</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="113">
@@ -17687,7 +17687,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E142" s="5" t="n">
         <v>0.068</v>
       </c>

--- a/output/pdf_financials_xlsx/GDL.xlsx
+++ b/output/pdf_financials_xlsx/GDL.xlsx
@@ -2222,43 +2222,43 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>0.442</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.579</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.866</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>1.378</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.759</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.325</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.152</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.311</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.137</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>0.396</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="41">
@@ -2268,43 +2268,43 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>72.83799999999999</v>
+        <v>73.28</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>60.591</v>
+        <v>61.17</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>65.67</v>
+        <v>66.536</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>64.255</v>
+        <v>65.633</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>57.607</v>
+        <v>58.366</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>50.008</v>
+        <v>50.333</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>50.008</v>
+        <v>50.818</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>63.246</v>
+        <v>63.398</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>63.246</v>
+        <v>63.407</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>64.423</v>
+        <v>64.73399999999999</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>53.674</v>
+        <v>53.811</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>56.601</v>
+        <v>56.997</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>55.471</v>
+        <v>56.211</v>
       </c>
     </row>
     <row r="42">
@@ -2590,43 +2590,43 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.433</v>
+        <v>2.991</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.271</v>
+        <v>2.692</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4.156</v>
+        <v>3.29</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>11.461</v>
+        <v>10.083</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>4.424</v>
+        <v>3.665</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3.143</v>
+        <v>2.818</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>3.143</v>
+        <v>2.333</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>4.189</v>
+        <v>4.037</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>4.189</v>
+        <v>4.028</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>4.994</v>
+        <v>4.683</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>10.501</v>
+        <v>10.364</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>10.681</v>
+        <v>10.285</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>4.528</v>
+        <v>3.788</v>
       </c>
     </row>
     <row r="49">
@@ -5728,13 +5728,13 @@
         <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.039</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.033</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.054</v>
       </c>
       <c r="L116" s="3" t="n">
         <v>0</v>
@@ -5743,7 +5743,7 @@
         <v>0</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="117">
@@ -6032,16 +6032,16 @@
         <v>0</v>
       </c>
       <c r="C123" s="3" t="n">
-        <v>0</v>
+        <v>0.909</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>0</v>
+        <v>0.369</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>0</v>
+        <v>0.068</v>
       </c>
       <c r="G123" s="3" t="n">
         <v>0</v>
@@ -6124,16 +6124,16 @@
         <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>0.909</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>0.369</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>0.068</v>
       </c>
       <c r="G125" s="3" t="n">
         <v>0</v>
@@ -17610,7 +17610,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -20528,7 +20532,11 @@
           <t>Acquisition in intangible assets</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -25689,7 +25697,11 @@
           <t>Increase in long-term debt</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -33422,7 +33434,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
